--- a/modbus_register_map.xlsx
+++ b/modbus_register_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\ST\projects\h523-obd-can\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B066EFF0-103B-43B0-8782-38CC8B0A1110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56424862-E169-49B3-973D-F6EFC6F4E809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="330" windowWidth="29040" windowHeight="15990" xr2:uid="{D7E73764-C2CD-4ED2-B9B8-2B2D11593FE5}"/>
+    <workbookView xWindow="28680" yWindow="2550" windowWidth="29040" windowHeight="15990" xr2:uid="{D7E73764-C2CD-4ED2-B9B8-2B2D11593FE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>data</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>accelerometer Z</t>
+  </si>
+  <si>
+    <t>total g</t>
   </si>
 </sst>
 </file>
@@ -860,6 +863,12 @@
         <f t="shared" si="3"/>
         <v>108</v>
       </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>1000</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
